--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -6,6 +6,7 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>Table</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Total Claim Cost 2</t>
   </si>
   <si>
-    <t>Toatl FullProfit Premium 2</t>
+    <t>Total FullProfit Premium 2</t>
   </si>
   <si>
     <t>Total ZeroProfit Premium 2</t>
@@ -42,7 +43,7 @@
     <t>Total Claim Cost</t>
   </si>
   <si>
-    <t>Toatl FullProfit Premium</t>
+    <t>Total FullProfit Premium</t>
   </si>
   <si>
     <t>Total ZeroProfit Premium</t>
@@ -52,6 +53,12 @@
   </si>
   <si>
     <t>Total Base Claim Cost 2</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
   </si>
 </sst>
 </file>
@@ -109,6 +116,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -550,4 +561,32 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1">
+        <v>30000.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>Table</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Annual Total Cost</t>
   </si>
 </sst>
 </file>
@@ -586,6 +589,14 @@
         <v>30000.0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2688.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
